--- a/ThesisStudy2Exp1a_Stim.xlsx
+++ b/ThesisStudy2Exp1a_Stim.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nicktarantino/Desktop/ThesisProject_Study2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B561531-A6EE-8F47-85E1-44C4C7295332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{794E8AA7-5947-EA49-AD87-56AB0674B85C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2600" yWindow="5420" windowWidth="30240" windowHeight="17340" xr2:uid="{06672470-1C49-BD45-B6D2-6C4308579EC0}"/>
+    <workbookView xWindow="0" yWindow="4880" windowWidth="30240" windowHeight="17340" xr2:uid="{06672470-1C49-BD45-B6D2-6C4308579EC0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -446,10 +446,10 @@
         <v>5</v>
       </c>
       <c r="D9">
+        <v>7.5</v>
+      </c>
+      <c r="E9">
         <v>10</v>
-      </c>
-      <c r="E9">
-        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
@@ -466,11 +466,11 @@
       </c>
       <c r="D10">
         <f>D9-1</f>
-        <v>9</v>
+        <v>6.5</v>
       </c>
       <c r="E10">
         <f>E9-1</f>
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
@@ -487,11 +487,11 @@
       </c>
       <c r="D11">
         <f>D9+1</f>
-        <v>11</v>
+        <v>8.5</v>
       </c>
       <c r="E11">
         <f>E9+1</f>
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
@@ -508,11 +508,11 @@
       </c>
       <c r="D13" s="1">
         <f t="shared" si="0"/>
+        <v>0.13165249758739583</v>
+      </c>
+      <c r="E13" s="1">
+        <f t="shared" si="0"/>
         <v>0.17632698070846498</v>
-      </c>
-      <c r="E13" s="1">
-        <f t="shared" si="0"/>
-        <v>0.36397023426620234</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
@@ -529,11 +529,11 @@
       </c>
       <c r="D14" s="1">
         <f t="shared" si="0"/>
+        <v>0.11393560830164549</v>
+      </c>
+      <c r="E14" s="1">
+        <f t="shared" si="0"/>
         <v>0.15838444032453627</v>
-      </c>
-      <c r="E14" s="1">
-        <f t="shared" si="0"/>
-        <v>0.34432761328966527</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
@@ -550,11 +550,11 @@
       </c>
       <c r="D15" s="1">
         <f t="shared" si="0"/>
+        <v>0.14945100134912781</v>
+      </c>
+      <c r="E15" s="1">
+        <f t="shared" si="0"/>
         <v>0.19438030913771848</v>
-      </c>
-      <c r="E15" s="1">
-        <f t="shared" si="0"/>
-        <v>0.38386403503541577</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
@@ -571,11 +571,11 @@
       </c>
       <c r="D16" s="2">
         <f>D15-D14</f>
-        <v>3.5995868813182202E-2</v>
+        <v>3.5515393047482316E-2</v>
       </c>
       <c r="E16" s="2">
         <f>E15-E14</f>
-        <v>3.9536421745750505E-2</v>
+        <v>3.5995868813182202E-2</v>
       </c>
     </row>
   </sheetData>

--- a/ThesisStudy2Exp1a_Stim.xlsx
+++ b/ThesisStudy2Exp1a_Stim.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nicktarantino/Desktop/ThesisProject_Study2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{794E8AA7-5947-EA49-AD87-56AB0674B85C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4BBCC85-1178-AE41-92D4-1E68C654AA74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="4880" windowWidth="30240" windowHeight="17340" xr2:uid="{06672470-1C49-BD45-B6D2-6C4308579EC0}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17340" xr2:uid="{06672470-1C49-BD45-B6D2-6C4308579EC0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
